--- a/apps/web/public/importmallar/importmall-kunder.xlsx
+++ b/apps/web/public/importmallar/importmall-kunder.xlsx
@@ -82,7 +82,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Kundens e-postadress, max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt med en varning.</t>
+          <t xml:space="preserve">Kundens e-postadress, max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt på en ny post och orört på en befintlig, med en varning.</t>
         </r>
       </text>
     </comment>
@@ -226,7 +226,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Kundens generella rabatt i procent, 0–100, decimalkomma eller punkt. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Kundens generella rabatt i procent, 0–100, decimalkomma eller punkt. Skriv bara talet — 10 betyder 10 %; skriv inte procenttecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </r>
       </text>
     </comment>
@@ -238,7 +238,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false. Nej betyder att radens fakturaadresskolumner (namn, adress, postnummer, postort, land) ignoreras — kunden faktureras på besöksadressen; Ja eller tom cell använder dem som de är. Lagras inte.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false. Nej betyder att radens fakturaadresskolumner (namn, adress, postnummer, postort, land) ignoreras — en ny kund får ingen fakturaadress och en befintlig kunds sparade fakturaadress ändras inte. Ja eller tom cell använder kolumnerna som de är. Lagras inte.</t>
         </r>
       </text>
     </comment>
@@ -334,7 +334,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">E-postadress som fakturor skickas till, max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt med en varning.</t>
+          <t xml:space="preserve">E-postadress som fakturor skickas till, max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt på en ny post och orört på en befintlig, med en varning.</t>
         </r>
       </text>
     </comment>
@@ -425,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -434,6 +434,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,34 +446,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1" style="4"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1" style="4"/>
+    <col min="4" max="4" width="14" customWidth="1" style="4"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1" style="4"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1" style="4"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="21" customWidth="1"/>
-    <col min="15" max="15" width="19" customWidth="1"/>
-    <col min="16" max="16" width="25" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="14" max="14" width="21" customWidth="1" style="4"/>
+    <col min="15" max="15" width="19" customWidth="1" style="4"/>
+    <col min="16" max="16" width="25" customWidth="1" style="4"/>
+    <col min="17" max="17" width="14" customWidth="1" style="4"/>
+    <col min="18" max="18" width="18" customWidth="1" style="4"/>
     <col min="19" max="19" width="27" customWidth="1"/>
     <col min="20" max="20" width="15" customWidth="1"/>
     <col min="21" max="21" width="17" customWidth="1"/>
     <col min="22" max="22" width="22" customWidth="1"/>
     <col min="23" max="23" width="22" customWidth="1"/>
-    <col min="24" max="24" width="21" customWidth="1"/>
+    <col min="24" max="24" width="21" customWidth="1" style="4"/>
     <col min="25" max="25" width="18" customWidth="1"/>
     <col min="26" max="26" width="15" customWidth="1"/>
     <col min="27" max="27" width="22" customWidth="1"/>
-    <col min="28" max="28" width="26" customWidth="1"/>
+    <col min="28" max="28" width="26" customWidth="1" style="4"/>
     <col min="29" max="29" width="19" customWidth="1"/>
     <col min="30" max="30" width="16" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
@@ -668,88 +669,73 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolumner du inte behöver kan tas bort eller lämnas tomma, och kolumnernas ordning spelar ingen roll.</t>
+          <t xml:space="preserve">Ta bort kolumner du inte använder. Kolumnernas ordning spelar ingen roll.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">En tom cell lämnar normalt värdet orört på en befintlig post, utom i kolumner där tomt betyder något: Huvudleverantör och Staffel: från antal/Staffel: pris (Inköpspriser), Partiformningsregel (Artiklar) samt Kalkyl och Tidsenhet med Uppdatera befintliga operationer (Operationer). Vad tomt betyder står vid varje kolumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tal skrivs med decimalkomma eller punkt. Obligatoriska kolumner måste finnas med och vara ifyllda på varje rad.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kolumn</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorisk</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förklaring</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kundnummer</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ja</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kundens unika nummer, max 50 tecken. Finns numret redan uppdateras kunden, annars skapas en ny. Nummerserien för kunder flyttas fram förbi filens högsta rent numeriska nummer.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Namn</t>
+          <t xml:space="preserve">Kundnummer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kundens namn, max 255 tecken. Krävs för nya kunder. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Kundens unika nummer, max 50 tecken. Finns numret redan uppdateras kunden, annars skapas en ny. Nummerserien för kunder flyttas fram förbi filens högsta rent numeriska nummer.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Restaurang Exempelkrogen AB</t>
+          <t xml:space="preserve">1001</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organisationsnummer</t>
+          <t xml:space="preserve">Namn</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -759,19 +745,19 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 20 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Kundens namn, max 255 tecken. Krävs för nya kunder. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">556123-4567</t>
+          <t xml:space="preserve">Restaurang Exempelkrogen AB</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAT-nummer</t>
+          <t xml:space="preserve">Organisationsnummer</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -781,19 +767,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Momsregistreringsnummer, max 30 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Max 20 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE556123456701</t>
+          <t xml:space="preserve">556123-4567</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kontaktperson</t>
+          <t xml:space="preserve">VAT-nummer</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -803,19 +789,19 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kontaktpersonens namn på kundkortets Allmänt-flik, max 255 tecken — kontaktregistret importeras separat som kundkontakter.</t>
+          <t xml:space="preserve">Momsregistreringsnummer, max 30 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anna Andersson</t>
+          <t xml:space="preserve">SE556123456701</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">E-post</t>
+          <t xml:space="preserve">Kontaktperson</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -825,19 +811,19 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kundens e-postadress, max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt med en varning.</t>
+          <t xml:space="preserve">Kontaktpersonens namn på kundkortets Allmänt-flik, max 255 tecken — kontaktregistret importeras separat som kundkontakter.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">info@example.com</t>
+          <t xml:space="preserve">Anna Andersson</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telefon</t>
+          <t xml:space="preserve">E-post</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -847,19 +833,19 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 50 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Kundens e-postadress, max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt på en ny post och orört på en befintlig, med en varning.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010-200 10 10</t>
+          <t xml:space="preserve">info@example.com</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adress</t>
+          <t xml:space="preserve">Telefon</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -869,19 +855,19 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Besöksadressens första rad. Adress, Adressrad 2 och Adressrad 3 slås ihop till en adress med radbrytningar; är alla tre tomma lämnas adressen orörd.</t>
+          <t xml:space="preserve">Max 50 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storgatan 8</t>
+          <t xml:space="preserve">010-200 10 10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adressrad 2</t>
+          <t xml:space="preserve">Adress</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -891,19 +877,19 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Besöksadressens andra rad, valfri — slås ihop med Adress.</t>
+          <t xml:space="preserve">Besöksadressens första rad. Adress, Adressrad 2 och Adressrad 3 slås ihop till en adress med radbrytningar; är alla tre tomma lämnas adressen orörd.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hus B</t>
+          <t xml:space="preserve">Storgatan 8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adressrad 3</t>
+          <t xml:space="preserve">Adressrad 2</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -913,19 +899,19 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Besöksadressens tredje rad, valfri — slås ihop med Adress.</t>
+          <t xml:space="preserve">Besöksadressens andra rad, valfri — slås ihop med Adress.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingång 2</t>
+          <t xml:space="preserve">Hus B</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postnummer</t>
+          <t xml:space="preserve">Adressrad 3</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -935,19 +921,19 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 20 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Besöksadressens tredje rad, valfri — slås ihop med Adress.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123 50</t>
+          <t xml:space="preserve">Ingång 2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postort</t>
+          <t xml:space="preserve">Postnummer</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -957,19 +943,19 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 100 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Max 20 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exempelby</t>
+          <t xml:space="preserve">123 50</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Land</t>
+          <t xml:space="preserve">Postort</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -979,19 +965,19 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landskod med två bokstäver (t.ex. SE, NO, DK, DE); små bokstäver godtas. Tom cell ger SE för nya kunder och lämnar befintliga orörda.</t>
+          <t xml:space="preserve">Max 100 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE</t>
+          <t xml:space="preserve">Exempelby</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betalningsvillkor</t>
+          <t xml:space="preserve">Land</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1001,19 +987,19 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betalningsvillkorets kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som nytt villkor; börjar namnet med ett antal dagar (30 dagar netto) blir dagarna villkorets kod.</t>
+          <t xml:space="preserve">Landskod med två bokstäver (t.ex. SE, NO, DK, DE); små bokstäver godtas. Tom cell ger SE för nya kunder och lämnar befintliga orörda.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 dagar netto</t>
+          <t xml:space="preserve">SE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leveransvillkor</t>
+          <t xml:space="preserve">Betalningsvillkor</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1023,19 +1009,19 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leveransvillkorets kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som nytt villkor.</t>
+          <t xml:space="preserve">Betalningsvillkorets kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som nytt villkor; börjar namnet med ett antal dagar (30 dagar netto) blir dagarna villkorets kod.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fritt vårt lager</t>
+          <t xml:space="preserve">30 dagar netto</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leveranssätt/speditör</t>
+          <t xml:space="preserve">Leveransvillkor</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1045,19 +1031,19 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Speditörens kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som ny speditör.</t>
+          <t xml:space="preserve">Leveransvillkorets kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som nytt villkor.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exempelfrakt</t>
+          <t xml:space="preserve">Fritt vårt lager</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prislista</t>
+          <t xml:space="preserve">Leveranssätt/speditör</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1067,19 +1053,19 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prislistans kod eller namn (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som ny prislista.</t>
+          <t xml:space="preserve">Speditörens kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som ny speditör.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grossist</t>
+          <t xml:space="preserve">Exempelfrakt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kundrabatt (%)</t>
+          <t xml:space="preserve">Prislista</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1089,19 +1075,19 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kundens generella rabatt i procent, 0–100, decimalkomma eller punkt. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Prislistans kod eller namn (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som ny prislista.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">Grossist</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Avvikande fakturaadress</t>
+          <t xml:space="preserve">Kundrabatt (%)</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1111,19 +1097,19 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false. Nej betyder att radens fakturaadresskolumner (namn, adress, postnummer, postort, land) ignoreras — kunden faktureras på besöksadressen; Ja eller tom cell använder dem som de är. Lagras inte.</t>
+          <t xml:space="preserve">Kundens generella rabatt i procent, 0–100, decimalkomma eller punkt. Skriv bara talet — 10 betyder 10 %; skriv inte procenttecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fakturanamn</t>
+          <t xml:space="preserve">Avvikande fakturaadress</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1133,19 +1119,19 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Namnet på fakturan när det skiljer sig från kundens namn, max 255 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false. Nej betyder att radens fakturaadresskolumner (namn, adress, postnummer, postort, land) ignoreras — en ny kund får ingen fakturaadress och en befintlig kunds sparade fakturaadress ändras inte. Ja eller tom cell använder kolumnerna som de är. Lagras inte.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exempelkrogen AB, ekonomiavdelningen</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fakturaadress</t>
+          <t xml:space="preserve">Fakturanamn</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1155,19 +1141,19 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fakturaadressens första rad. Fakturaadress, Fakturaadressrad 2 och Fakturaadressrad 3 slås ihop med radbrytningar; är alla tre tomma lämnas fakturaadressen orörd.</t>
+          <t xml:space="preserve">Namnet på fakturan när det skiljer sig från kundens namn, max 255 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box 100</t>
+          <t xml:space="preserve">Exempelkrogen AB, ekonomiavdelningen</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fakturaadressrad 2</t>
+          <t xml:space="preserve">Fakturaadress</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1177,19 +1163,19 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fakturaadressens andra rad, valfri — slås ihop med Fakturaadress.</t>
+          <t xml:space="preserve">Fakturaadressens första rad. Fakturaadress, Fakturaadressrad 2 och Fakturaadressrad 3 slås ihop med radbrytningar; är alla tre tomma lämnas fakturaadressen orörd.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Att: Ekonomi</t>
+          <t xml:space="preserve">Box 100</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fakturaadressrad 3</t>
+          <t xml:space="preserve">Fakturaadressrad 2</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1199,19 +1185,19 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fakturaadressens tredje rad, valfri — slås ihop med Fakturaadress.</t>
+          <t xml:space="preserve">Fakturaadressens andra rad, valfri — slås ihop med Fakturaadress.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Våning 3</t>
+          <t xml:space="preserve">Att: Ekonomi</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fakturapostnummer</t>
+          <t xml:space="preserve">Fakturaadressrad 3</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1221,19 +1207,19 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 20 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Fakturaadressens tredje rad, valfri — slås ihop med Fakturaadress.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123 51</t>
+          <t xml:space="preserve">Våning 3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fakturapostort</t>
+          <t xml:space="preserve">Fakturapostnummer</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1243,19 +1229,19 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 100 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Max 20 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exempelby</t>
+          <t xml:space="preserve">123 51</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fakturaland</t>
+          <t xml:space="preserve">Fakturapostort</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1265,19 +1251,19 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landskod med två bokstäver (t.ex. SE); små bokstäver godtas. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Max 100 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE</t>
+          <t xml:space="preserve">Exempelby</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">E-post för faktura</t>
+          <t xml:space="preserve">Fakturaland</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1287,19 +1273,19 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">E-postadress som fakturor skickas till, max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt med en varning.</t>
+          <t xml:space="preserve">Landskod med två bokstäver (t.ex. SE); små bokstäver godtas. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">faktura@example.com</t>
+          <t xml:space="preserve">SE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vårt leverantörsnummer</t>
+          <t xml:space="preserve">E-post för faktura</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1309,19 +1295,19 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Det nummer kunden har på oss som leverantör, max 50 tecken — skrivs ut på offert, orderbekräftelse och faktura.</t>
+          <t xml:space="preserve">E-postadress som fakturor skickas till, max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt på en ny post och orört på en befintlig, med en varning.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">L-4711</t>
+          <t xml:space="preserve">faktura@example.com</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samlingsfaktura</t>
+          <t xml:space="preserve">Vårt leverantörsnummer</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1331,19 +1317,19 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — Ja gör att kundens leveranser faktureras genom samlingsfakturering; ett värde som börjar med Per (t.ex. Per kund) räknas också som Ja. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Det nummer kunden har på oss som leverantör, max 50 tecken — skrivs ut på offert, orderbekräftelse och faktura.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">L-4711</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Privatperson</t>
+          <t xml:space="preserve">Samlingsfaktura</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1353,7 +1339,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — Ja visar priser inklusive moms på kundens offerter, orderbekräftelser och fakturor. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — Ja gör att kundens leveranser faktureras genom samlingsfakturering; ett värde som börjar med Per (t.ex. Per kund) räknas också som Ja. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1365,20 +1351,42 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Privatperson</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — Ja visar priser inklusive moms på kundens offerter, orderbekräftelser och fakturor. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Webbsida</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nej</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Max 255 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.example.com</t>
         </is>

--- a/apps/web/public/importmallar/importmall-kunder.xlsx
+++ b/apps/web/public/importmallar/importmall-kunder.xlsx
@@ -383,6 +383,18 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Max 255 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AF1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Valutakod med tre bokstäver (SEK, EUR, NOK …); små bokstäver godtas, annat ger ett fel. Nya offerter och kundordrar får kundens valuta och dagens kurs, och kundens kundpriser gäller i den valutan; befintliga ordrar behåller sin. Tom cell ger SEK för nya kunder och lämnar befintliga orörda.</t>
         </r>
       </text>
     </comment>
@@ -477,6 +489,7 @@
     <col min="29" max="29" width="19" customWidth="1"/>
     <col min="30" max="30" width="16" customWidth="1"/>
     <col min="31" max="31" width="14" customWidth="1"/>
+    <col min="32" max="32" width="14" customWidth="1" style="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,6 +646,11 @@
       <c r="AE1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Webbsida</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valuta</t>
         </is>
       </c>
     </row>
@@ -1392,6 +1410,28 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valuta</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valutakod med tre bokstäver (SEK, EUR, NOK …); små bokstäver godtas, annat ger ett fel. Nya offerter och kundordrar får kundens valuta och dagens kurs, och kundens kundpriser gäller i den valutan; befintliga ordrar behåller sin. Tom cell ger SEK för nya kunder och lämnar befintliga orörda.</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/apps/web/public/importmallar/importmall-kunder.xlsx
+++ b/apps/web/public/importmallar/importmall-kunder.xlsx
@@ -370,11 +370,23 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — Ja betyder att kundens fakturor granskas före utskick: samlingsfaktureringens Utfärda direkt lämnar dem som utkast. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AE1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — Ja visar priser inklusive moms på kundens offerter, orderbekräftelser och fakturor. Tom cell lämnar fältet orört på en befintlig post.</t>
         </r>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0">
+    <comment ref="AF1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -386,7 +398,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF1" authorId="0">
+    <comment ref="AG1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -487,9 +499,10 @@
     <col min="27" max="27" width="22" customWidth="1"/>
     <col min="28" max="28" width="26" customWidth="1" style="4"/>
     <col min="29" max="29" width="19" customWidth="1"/>
-    <col min="30" max="30" width="16" customWidth="1"/>
-    <col min="31" max="31" width="14" customWidth="1"/>
-    <col min="32" max="32" width="14" customWidth="1" style="4"/>
+    <col min="30" max="30" width="23" customWidth="1"/>
+    <col min="31" max="31" width="16" customWidth="1"/>
+    <col min="32" max="32" width="14" customWidth="1"/>
+    <col min="33" max="33" width="14" customWidth="1" style="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -640,15 +653,20 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Faktura i vänteläge</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Privatperson</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Webbsida</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Valuta</t>
         </is>
@@ -1369,7 +1387,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Privatperson</t>
+          <t xml:space="preserve">Faktura i vänteläge</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1379,7 +1397,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — Ja visar priser inklusive moms på kundens offerter, orderbekräftelser och fakturor. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — Ja betyder att kundens fakturor granskas före utskick: samlingsfaktureringens Utfärda direkt lämnar dem som utkast. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1391,7 +1409,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Webbsida</t>
+          <t xml:space="preserve">Privatperson</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1401,32 +1419,54 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 255 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Ja/Nej, 1/0, X eller true/false — Ja visar priser inklusive moms på kundens offerter, orderbekräftelser och fakturor. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.example.com</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Webbsida</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Max 255 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Valuta</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nej</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Valutakod med tre bokstäver (SEK, EUR, NOK …); små bokstäver godtas, annat ger ett fel. Nya offerter och kundordrar får kundens valuta och dagens kurs, och kundens kundpriser gäller i den valutan; befintliga ordrar behåller sin. Tom cell ger SEK för nya kunder och lämnar befintliga orörda.</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SEK</t>
         </is>
